--- a/experiments/02_term_expansion_by_language_pair/report/dev_v1_cleaned_language_comparison.xlsx
+++ b/experiments/02_term_expansion_by_language_pair/report/dev_v1_cleaned_language_comparison.xlsx
@@ -568,28 +568,28 @@
   <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/experiments/02_term_expansion_by_language_pair/report/dev_v1_cleaned_language_comparison.xlsx
+++ b/experiments/02_term_expansion_by_language_pair/report/dev_v1_cleaned_language_comparison.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,11 @@
       <b val="1"/>
     </font>
     <font/>
+    <font>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,14 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
-        <bgColor rgb="00F8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
-        <bgColor rgb="00BDD7EE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -173,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -184,20 +181,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1012,7 +1003,7 @@
       <c r="Q6" s="5" t="n">
         <v>0.9724740321057601</v>
       </c>
-      <c r="R6" s="10" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
@@ -1026,7 +1017,7 @@
       <c r="U6" s="5" t="n">
         <v>0.9215686274509802</v>
       </c>
-      <c r="V6" s="10" t="inlineStr">
+      <c r="V6" s="6" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
@@ -1090,7 +1081,7 @@
       <c r="Q7" s="5" t="n">
         <v>0.9704640496425198</v>
       </c>
-      <c r="R7" s="10" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
@@ -1104,7 +1095,7 @@
       <c r="U7" s="5" t="n">
         <v>0.9150326797385622</v>
       </c>
-      <c r="V7" s="10" t="inlineStr">
+      <c r="V7" s="6" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
@@ -1168,7 +1159,7 @@
       <c r="Q8" s="8" t="n">
         <v>0.9720018885741264</v>
       </c>
-      <c r="R8" s="11" t="inlineStr">
+      <c r="R8" s="9" t="inlineStr">
         <is>
           <t>ende</t>
         </is>
@@ -1182,7 +1173,7 @@
       <c r="U8" s="8" t="n">
         <v>0.9215686274509802</v>
       </c>
-      <c r="V8" s="11" t="inlineStr">
+      <c r="V8" s="9" t="inlineStr">
         <is>
           <t>ende</t>
         </is>

--- a/experiments/02_term_expansion_by_language_pair/report/dev_v1_cleaned_language_comparison.xlsx
+++ b/experiments/02_term_expansion_by_language_pair/report/dev_v1_cleaned_language_comparison.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,11 @@
     <font>
       <color rgb="00006100"/>
     </font>
+    <font>
+      <color rgb="009C6500"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +55,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -170,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -189,6 +198,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1159,9 +1171,9 @@
       <c r="Q8" s="8" t="n">
         <v>0.9720018885741264</v>
       </c>
-      <c r="R8" s="9" t="inlineStr">
-        <is>
-          <t>ende</t>
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>tie</t>
         </is>
       </c>
       <c r="S8" s="8" t="n">
